--- a/ip6-validasyon/inceleme_kuyrugu_ilk50.xlsx
+++ b/ip6-validasyon/inceleme_kuyrugu_ilk50.xlsx
@@ -456,260 +456,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9509110</t>
+          <t>1701232</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sosyal Sorumluluk Uygulamaları</t>
+          <t>Araştırma Projesi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eğitim</t>
+          <t>Spor Bilimleri</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>24.5566</v>
+        <v>11.2826</v>
       </c>
       <c r="F2" t="n">
-        <v>718.55</v>
+        <v>276.09</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=3.0 | rf_tahmin=33.31 | kural_akts=4.12 (K_bilissel=1.03, K_profil=1.20, K_etkinlik=1.11) | adaptif=24.56 | sapma=+718.5%</t>
+          <t>AKTS_mevcut=3.0 | model_tahmin=14.29 | kural_akts=4.27 (K_bilissel=1.10, K_profil=1.20, K_etkinlik=1.08) | adaptif=11.28 | sapma=+276.1%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9509084</t>
+          <t>207536</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bilişim Teknolojileri</t>
+          <t>Sayısal Tasarım Laboratuvarı</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eğitim</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>24.3021</v>
+        <v>3.6051</v>
       </c>
       <c r="F3" t="n">
-        <v>507.55</v>
+        <v>260.51</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=31.84 | kural_akts=6.70 (K_bilissel=1.16, K_profil=1.30, K_etkinlik=1.11) | adaptif=24.30 | sapma=+507.6%</t>
+          <t>AKTS_mevcut=1.0 | model_tahmin=4.54 | kural_akts=1.43 (K_bilissel=1.31, K_profil=1.10, K_etkinlik=0.99) | adaptif=3.61 | sapma=+260.5%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>715187</t>
+          <t>103381</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AHŞAP ATÖLYESİ 2</t>
+          <t>Bitirme Çalışması</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>22.2383</v>
+        <v>2.8331</v>
       </c>
       <c r="F4" t="n">
-        <v>455.96</v>
+        <v>183.31</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=29.77 | kural_akts=4.66 (K_bilissel=1.00, K_profil=1.05, K_etkinlik=1.11) | adaptif=22.24 | sapma=+456.0%</t>
+          <t>AKTS_mevcut=1.0 | model_tahmin=3.49 | kural_akts=1.31 (K_bilissel=1.32, K_profil=1.00, K_etkinlik=0.99) | adaptif=2.83 | sapma=+183.3%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1701232</t>
+          <t>711070</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Araştırma Projesi</t>
+          <t>Bitirme Çalışması</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spor Bilimleri</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>11.3965</v>
+        <v>4.8777</v>
       </c>
       <c r="F5" t="n">
-        <v>279.88</v>
+        <v>143.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=3.0 | rf_tahmin=14.45 | kural_akts=4.27 (K_bilissel=1.10, K_profil=1.20, K_etkinlik=1.08) | adaptif=11.40 | sapma=+279.9%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=5.75 | kural_akts=2.85 (K_bilissel=1.37, K_profil=1.05, K_etkinlik=0.99) | adaptif=4.88 | sapma=+143.9%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>207536</t>
+          <t>731005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sayısal Tasarım Laboratuvarı</t>
+          <t>Teknik Çizim Perspektif I</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7055</v>
+        <v>2.4238</v>
       </c>
       <c r="F6" t="n">
-        <v>270.55</v>
+        <v>142.38</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=1.0 | rf_tahmin=4.68 | kural_akts=1.43 (K_bilissel=1.31, K_profil=1.10, K_etkinlik=0.99) | adaptif=3.71 | sapma=+270.6%</t>
+          <t>AKTS_mevcut=1.0 | model_tahmin=3.04 | kural_akts=0.99 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=2.42 | sapma=+142.4%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>711070</t>
+          <t>9509115</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bitirme Çalışması</t>
+          <t>Üniversite ve Yaşam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Eğitim</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>7.3389</v>
+        <v>7.136</v>
       </c>
       <c r="F7" t="n">
-        <v>266.94</v>
+        <v>137.87</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=9.26 | kural_akts=2.85 (K_bilissel=1.37, K_profil=1.05, K_etkinlik=0.99) | adaptif=7.34 | sapma=+266.9%</t>
+          <t>AKTS_mevcut=3.0 | model_tahmin=8.86 | kural_akts=3.11 (K_bilissel=1.00, K_profil=1.05, K_etkinlik=0.99) | adaptif=7.14 | sapma=+137.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>731005</t>
+          <t>113108</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teknik Çizim Perspektif I</t>
+          <t>Mesleki İngilizce I</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7842</v>
+        <v>4.6934</v>
       </c>
       <c r="F8" t="n">
-        <v>178.42</v>
+        <v>134.67</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=1.0 | rf_tahmin=3.55 | kural_akts=0.99 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=2.78 | sapma=+178.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=5.67 | kural_akts=2.40 (K_bilissel=1.18, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.69 | sapma=+134.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2105340</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PSİKOLOJİ</t>
+          <t>Çağdaş Grafik Tasarım Tarihi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spor Bilimleri</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>7.986</v>
+        <v>4.6803</v>
       </c>
       <c r="F9" t="n">
-        <v>166.2</v>
+        <v>134.01</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=3.0 | rf_tahmin=9.67 | kural_akts=4.05 (K_bilissel=1.06, K_profil=1.15, K_etkinlik=1.11) | adaptif=7.99 | sapma=+166.2%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=5.73 | kural_akts=2.24 (K_bilissel=1.10, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.68 | sapma=+134.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9507003</t>
+          <t>713167</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teknik Çizim ve Perspektif-I</t>
+          <t xml:space="preserve">Desen ve Anatomi I </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -721,26 +721,26 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3183</v>
+        <v>4.2967</v>
       </c>
       <c r="F10" t="n">
-        <v>165.92</v>
+        <v>114.84</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=6.71 | kural_akts=2.08 (K_bilissel=1.05, K_profil=1.00, K_etkinlik=0.99) | adaptif=5.32 | sapma=+165.9%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=5.18 | kural_akts=2.24 (K_bilissel=1.07, K_profil=1.00, K_etkinlik=1.05) | adaptif=4.30 | sapma=+114.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>721127</t>
+          <t>9507021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tipografi Yazı III</t>
+          <t>Doğa Fotoğrafı</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -749,60 +749,60 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4294</v>
+        <v>4.2231</v>
       </c>
       <c r="F11" t="n">
-        <v>160.74</v>
+        <v>111.16</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=12.69 | kural_akts=5.15 (K_bilissel=1.10, K_profil=1.15, K_etkinlik=1.02) | adaptif=10.43 | sapma=+160.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=5.10 | kural_akts=2.18 (K_bilissel=1.10, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.22 | sapma=+111.2%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>721018</t>
+          <t>215179</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tipografi Yazı-2</t>
+          <t>Proje Tasarım</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3426</v>
+        <v>4.1851</v>
       </c>
       <c r="F12" t="n">
-        <v>158.56</v>
+        <v>109.26</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=12.77 | kural_akts=4.69 (K_bilissel=1.00, K_profil=1.15, K_etkinlik=1.02) | adaptif=10.34 | sapma=+158.6%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.93 | kural_akts=2.46 (K_bilissel=1.08, K_profil=1.15, K_etkinlik=0.99) | adaptif=4.19 | sapma=+109.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>117204</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mesleki İngilizce I</t>
+          <t>Genel Ekoloji Lab.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -814,145 +814,145 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1627</v>
+        <v>4.1691</v>
       </c>
       <c r="F13" t="n">
-        <v>158.14</v>
+        <v>108.45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=6.34 | kural_akts=2.40 (K_bilissel=1.18, K_profil=1.00, K_etkinlik=1.02) | adaptif=5.16 | sapma=+158.1%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.96 | kural_akts=2.32 (K_bilissel=1.14, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.17 | sapma=+108.5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>727034</t>
+          <t>217409</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seminer</t>
+          <t>Makine Isıl Tasarım Projesi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9394</v>
+        <v>4.1021</v>
       </c>
       <c r="F14" t="n">
-        <v>146.97</v>
+        <v>105.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=6.23 | kural_akts=1.92 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.96) | adaptif=4.94 | sapma=+147.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.83 | kural_akts=2.41 (K_bilissel=1.00, K_profil=1.15, K_etkinlik=1.05) | adaptif=4.10 | sapma=+105.1%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>117255</t>
+          <t>215217</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Laboratuvar ve Mikroskop Teknikleri</t>
+          <t>Jeotermal Sistemler</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fen-Edebiyat</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8596</v>
+        <v>4.0898</v>
       </c>
       <c r="F15" t="n">
-        <v>142.98</v>
+        <v>104.49</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=6.09 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.86 | sapma=+143.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.79 | kural_akts=2.44 (K_bilissel=1.20, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.09 | sapma=+104.5%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>721135</t>
+          <t>205518</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tipografi Yazı IV</t>
+          <t xml:space="preserve">Mühendislikte Çizim </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>9.6677</v>
+        <v>4.0532</v>
       </c>
       <c r="F16" t="n">
-        <v>141.69</v>
+        <v>102.66</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=11.54 | kural_akts=5.31 (K_bilissel=1.13, K_profil=1.15, K_etkinlik=1.02) | adaptif=9.67 | sapma=+141.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.66 | kural_akts=2.64 (K_bilissel=1.18, K_profil=1.10, K_etkinlik=1.02) | adaptif=4.05 | sapma=+102.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>205662</t>
+          <t>117164</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elektrik Mühendisliği Projesi</t>
+          <t>Hayvan Anatomisi Lab.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4791</v>
+        <v>4.0484</v>
       </c>
       <c r="F17" t="n">
-        <v>123.96</v>
+        <v>102.42</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.21 | kural_akts=2.77 (K_bilissel=1.15, K_profil=1.15, K_etkinlik=1.05) | adaptif=4.48 | sapma=+124.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.75 | kural_akts=2.40 (K_bilissel=1.22, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.05 | sapma=+102.4%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>103381</t>
+          <t>107514</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -966,29 +966,29 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.234</v>
+        <v>4.0426</v>
       </c>
       <c r="F18" t="n">
-        <v>123.4</v>
+        <v>102.13</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=1.0 | rf_tahmin=2.63 | kural_akts=1.31 (K_bilissel=1.32, K_profil=1.00, K_etkinlik=0.99) | adaptif=2.23 | sapma=+123.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.67 | kural_akts=2.57 (K_bilissel=1.30, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.04 | sapma=+102.1%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9507021</t>
+          <t>719155</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Doğa Fotoğrafı</t>
+          <t>BELGESEL FOTOĞRAF-I</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -997,308 +997,308 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4628</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>123.14</v>
+        <v>101.07</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.44 | kural_akts=2.18 (K_bilissel=1.10, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.46 | sapma=+123.1%</t>
+          <t>AKTS_mevcut=4.0 | model_tahmin=8.80 | kural_akts=6.27 (K_bilissel=1.38, K_profil=1.05, K_etkinlik=1.08) | adaptif=8.04 | sapma=+101.1%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1307087</t>
+          <t>205662</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Programlama Laboratuvarı-II</t>
+          <t>Elektrik Mühendisliği Projesi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4407</v>
+        <v>4.0152</v>
       </c>
       <c r="F20" t="n">
-        <v>122.04</v>
+        <v>100.76</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.21 | kural_akts=2.65 (K_bilissel=1.27, K_profil=1.05, K_etkinlik=0.99) | adaptif=4.44 | sapma=+122.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.55 | kural_akts=2.77 (K_bilissel=1.15, K_profil=1.15, K_etkinlik=1.05) | adaptif=4.02 | sapma=+100.8%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9513058</t>
+          <t>207473</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>İşletmede Mesleki Eğitim (UE)</t>
+          <t>Analog Haberleşme Laboratuvarı</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>11.0017</v>
+        <v>4.0135</v>
       </c>
       <c r="F21" t="n">
-        <v>120.03</v>
+        <v>100.68</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=5.0 | rf_tahmin=12.83 | kural_akts=6.74 (K_bilissel=1.23, K_profil=1.05, K_etkinlik=1.05) | adaptif=11.00 | sapma=+120.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.77 | kural_akts=2.24 (K_bilissel=1.00, K_profil=1.10, K_etkinlik=1.02) | adaptif=4.01 | sapma=+100.7%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>213387</t>
+          <t>117172</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YER RADARI</t>
+          <t>Bitki Fizyolojisi Lab.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>4.3934</v>
+        <v>3.9901</v>
       </c>
       <c r="F22" t="n">
-        <v>119.67</v>
+        <v>99.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.11 | kural_akts=2.73 (K_bilissel=1.24, K_profil=1.05, K_etkinlik=1.05) | adaptif=4.39 | sapma=+119.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.78 | kural_akts=2.15 (K_bilissel=1.09, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.99 | sapma=+99.5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>727034</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bitki Fizyolojisi Lab.</t>
+          <t>Seminer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fen-Edebiyat</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4.3879</v>
+        <v>3.9658</v>
       </c>
       <c r="F23" t="n">
-        <v>119.4</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.35 | kural_akts=2.15 (K_bilissel=1.09, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.39 | sapma=+119.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.84 | kural_akts=1.92 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.96) | adaptif=3.97 | sapma=+98.3%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9507010</t>
+          <t>105180</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fotoğraf Sanatı Tarihi</t>
+          <t>Seminer II</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3705</v>
+        <v>3.9597</v>
       </c>
       <c r="F24" t="n">
-        <v>118.52</v>
+        <v>97.98</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.16 | kural_akts=2.53 (K_bilissel=1.28, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.37 | sapma=+118.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.72 | kural_akts=2.18 (K_bilissel=1.04, K_profil=1.00, K_etkinlik=1.05) | adaptif=3.96 | sapma=+98.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>217409</t>
+          <t>9513055</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Makine Isıl Tasarım Projesi</t>
+          <t>İş Sağlığı ve Güvenliği</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Teknoloji</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>4.3545</v>
+        <v>3.8762</v>
       </c>
       <c r="F25" t="n">
-        <v>117.72</v>
+        <v>93.81</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.19 | kural_akts=2.41 (K_bilissel=1.00, K_profil=1.15, K_etkinlik=1.05) | adaptif=4.35 | sapma=+117.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.61 | kural_akts=2.15 (K_bilissel=1.06, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.88 | sapma=+93.8%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9513060</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>İşletmede Mesleki Eğitim (UE) Bahar</t>
+          <t>Mikrobiyoloji II Lab</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Teknoloji</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>10.7216</v>
+        <v>3.8521</v>
       </c>
       <c r="F26" t="n">
-        <v>114.43</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=5.0 | rf_tahmin=13.09 | kural_akts=5.19 (K_bilissel=1.05, K_profil=1.00, K_etkinlik=0.99) | adaptif=10.72 | sapma=+114.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.50 | kural_akts=2.34 (K_bilissel=1.15, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.85 | sapma=+92.6%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>713167</t>
+          <t>105149</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desen ve Anatomi I </t>
+          <t>Mesleki İngilizce II</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.2707</v>
+        <v>3.8448</v>
       </c>
       <c r="F27" t="n">
-        <v>113.54</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.14 | kural_akts=2.24 (K_bilissel=1.07, K_profil=1.00, K_etkinlik=1.05) | adaptif=4.27 | sapma=+113.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.61 | kural_akts=2.06 (K_bilissel=1.04, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.84 | sapma=+92.2%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>215179</t>
+          <t>105151</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Proje Tasarım</t>
+          <t>Mesleki İngilizce IV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>4.2382</v>
+        <v>3.8316</v>
       </c>
       <c r="F28" t="n">
-        <v>111.91</v>
+        <v>91.58</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.00 | kural_akts=2.46 (K_bilissel=1.08, K_profil=1.15, K_etkinlik=0.99) | adaptif=4.24 | sapma=+111.9%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.59 | kural_akts=2.06 (K_bilissel=1.04, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.83 | sapma=+91.6%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>117204</t>
+          <t>117162</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Genel Ekoloji Lab.</t>
+          <t>Histoloji Lab.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1310,181 +1310,181 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>4.2352</v>
+        <v>3.8198</v>
       </c>
       <c r="F29" t="n">
-        <v>111.76</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=5.05 | kural_akts=2.32 (K_bilissel=1.14, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.24 | sapma=+111.8%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.52 | kural_akts=2.18 (K_bilissel=1.02, K_profil=1.05, K_etkinlik=1.02) | adaptif=3.82 | sapma=+91.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>731010</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jeotermal Sistemler</t>
+          <t>Desen II</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.153</v>
+        <v>3.8168</v>
       </c>
       <c r="F30" t="n">
-        <v>107.65</v>
+        <v>90.84</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.88 | kural_akts=2.44 (K_bilissel=1.20, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.15 | sapma=+107.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.61 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.82 | sapma=+90.8%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>211386</t>
+          <t>1705008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ekonomi ve İnovasyon</t>
+          <t>İSTATİSTİK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Spor Bilimleri</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4.1207</v>
+        <v>3.8162</v>
       </c>
       <c r="F31" t="n">
-        <v>106.04</v>
+        <v>90.81</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.88 | kural_akts=2.34 (K_bilissel=1.00, K_profil=1.15, K_etkinlik=1.02) | adaptif=4.12 | sapma=+106.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.51 | kural_akts=2.19 (K_bilissel=1.07, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.82 | sapma=+90.8%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>207473</t>
+          <t>117255</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Analog Haberleşme Laboratuvarı</t>
+          <t>Laboratuvar ve Mikroskop Teknikleri</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>4.0852</v>
+        <v>3.8156</v>
       </c>
       <c r="F32" t="n">
-        <v>104.26</v>
+        <v>90.78</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.88 | kural_akts=2.24 (K_bilissel=1.00, K_profil=1.10, K_etkinlik=1.02) | adaptif=4.09 | sapma=+104.3%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.60 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.82 | sapma=+90.8%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>731010</t>
+          <t>105148</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Desen II</t>
+          <t>Mesleki İngilizce I</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.0708</v>
+        <v>3.8103</v>
       </c>
       <c r="F33" t="n">
-        <v>103.54</v>
+        <v>90.52</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.97 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.07 | sapma=+103.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.60 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.81 | sapma=+90.5%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>721117</t>
+          <t>215218</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Çağdaş Grafik Tasarım Tarihi</t>
+          <t>İklim Değişikliği ve Sürdürülebilirlik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4.0609</v>
+        <v>3.7993</v>
       </c>
       <c r="F34" t="n">
-        <v>103.05</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.84 | kural_akts=2.24 (K_bilissel=1.10, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.06 | sapma=+103.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.42 | kural_akts=2.34 (K_bilissel=1.15, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.80 | sapma=+90.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>729054</t>
+          <t>9507067</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dans I</t>
+          <t>Yayın Grafiği-I</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1496,88 +1496,88 @@
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>4.0558</v>
+        <v>3.7982</v>
       </c>
       <c r="F35" t="n">
-        <v>102.79</v>
+        <v>89.91</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.90 | kural_akts=2.08 (K_bilissel=1.05, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.06 | sapma=+102.8%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.55 | kural_akts=2.04 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.80 | sapma=+89.9%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>729055</t>
+          <t>107513</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dans II</t>
+          <t>Seminer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.0558</v>
+        <v>3.7818</v>
       </c>
       <c r="F36" t="n">
-        <v>102.79</v>
+        <v>89.09</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.90 | kural_akts=2.08 (K_bilissel=1.05, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.06 | sapma=+102.8%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.43 | kural_akts=2.26 (K_bilissel=1.14, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.78 | sapma=+89.1%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>721017</t>
+          <t>8201015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tipografi Yazı-1</t>
+          <t>Sosyal Bilimlerde Yöntem I</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Siyasal Bilgiler</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>8.1029</v>
+        <v>3.7813</v>
       </c>
       <c r="F37" t="n">
-        <v>102.57</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=4.0 | rf_tahmin=9.49 | kural_akts=4.87 (K_bilissel=1.04, K_profil=1.15, K_etkinlik=1.02) | adaptif=8.10 | sapma=+102.6%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.35 | kural_akts=2.44 (K_bilissel=1.20, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.78 | sapma=+89.1%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>217408</t>
+          <t>203505</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Makine Mekanik Tasarım Projesi</t>
+          <t>İş Sağlığı ve Güvenliği-I</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1589,88 +1589,88 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>4.0474</v>
+        <v>3.7767</v>
       </c>
       <c r="F38" t="n">
-        <v>102.37</v>
+        <v>88.84</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.93 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.05 | sapma=+102.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.23 | kural_akts=2.73 (K_bilissel=1.30, K_profil=1.00, K_etkinlik=1.05) | adaptif=3.78 | sapma=+88.8%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>105150</t>
+          <t>9507007</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mesleki İngilizce III</t>
+          <t>Teknik Çizim ve Perspektif-II</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fen-Edebiyat</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.0437</v>
+        <v>3.7655</v>
       </c>
       <c r="F39" t="n">
-        <v>102.18</v>
+        <v>88.28</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.87 | kural_akts=2.12 (K_bilissel=1.04, K_profil=1.00, K_etkinlik=1.02) | adaptif=4.04 | sapma=+102.2%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.38 | kural_akts=2.32 (K_bilissel=1.18, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.77 | sapma=+88.3%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>709204</t>
+          <t>211386</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tiyatro Tarihi ve Kuramları II</t>
+          <t>Ekonomi ve İnovasyon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>4.0341</v>
+        <v>3.7632</v>
       </c>
       <c r="F40" t="n">
-        <v>101.7</v>
+        <v>88.16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.98 | kural_akts=1.82 (K_bilissel=1.05, K_profil=1.00, K_etkinlik=0.87) | adaptif=4.03 | sapma=+101.7%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.37 | kural_akts=2.34 (K_bilissel=1.00, K_profil=1.15, K_etkinlik=1.02) | adaptif=3.76 | sapma=+88.2%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9507109</t>
+          <t>713176</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Müzikte Temel Kavramlar I</t>
+          <t>Sergi Hazırlama ve Küratoryel Çalışmalar II</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1682,57 +1682,57 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>4.0152</v>
+        <v>3.7612</v>
       </c>
       <c r="F41" t="n">
-        <v>100.76</v>
+        <v>88.06</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.79 | kural_akts=2.20 (K_bilissel=1.00, K_profil=1.05, K_etkinlik=1.05) | adaptif=4.02 | sapma=+100.8%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.31 | kural_akts=2.47 (K_bilissel=1.25, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.76 | sapma=+88.1%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>207506</t>
+          <t>713173</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mesleki İngilizce</t>
+          <t>Sergi Hazırlama ve Küratoryel Çalışmalar I</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.0118</v>
+        <v>3.7612</v>
       </c>
       <c r="F42" t="n">
-        <v>100.59</v>
+        <v>88.06</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.78 | kural_akts=2.21 (K_bilissel=1.12, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.01 | sapma=+100.6%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.31 | kural_akts=2.47 (K_bilissel=1.25, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.76 | sapma=+88.1%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>219200</t>
+          <t>213387</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Metalurji ve Malzeme Mühendisliğine Giriş</t>
+          <t>YER RADARI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1744,88 +1744,88 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>4.0108</v>
+        <v>3.7599</v>
       </c>
       <c r="F43" t="n">
-        <v>100.54</v>
+        <v>88</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.85 | kural_akts=2.04 (K_bilissel=1.03, K_profil=1.00, K_etkinlik=0.99) | adaptif=4.01 | sapma=+100.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.20 | kural_akts=2.73 (K_bilissel=1.24, K_profil=1.05, K_etkinlik=1.05) | adaptif=3.76 | sapma=+88.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>213306</t>
+          <t>9507010</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARKEOLOJİDE JEOFİZİK UYGULAMALAR</t>
+          <t>Fotoğraf Sanatı Tarihi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>3.9875</v>
+        <v>3.7598</v>
       </c>
       <c r="F44" t="n">
-        <v>99.38</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.78 | kural_akts=2.14 (K_bilissel=1.08, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.99 | sapma=+99.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.29 | kural_akts=2.53 (K_bilissel=1.28, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.76 | sapma=+88.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>213301</t>
+          <t>729050</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JEOTERMAL ARAMALARDA JEOFİZİK YÖNTEMLER</t>
+          <t>Şan ve Solfej</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mühendislik</t>
+          <t>Güzel Sanatlar</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.9708</v>
+        <v>3.7527</v>
       </c>
       <c r="F45" t="n">
-        <v>98.54000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.67 | kural_akts=2.34 (K_bilissel=1.18, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.97 | sapma=+98.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.49 | kural_akts=2.04 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.75 | sapma=+87.6%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>201389</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>İş Hayatı ve İş Güvenliğine Hazırlık</t>
+          <t>Makine Mekanik Tasarım Projesi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1837,26 +1837,26 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>3.97</v>
+        <v>3.7414</v>
       </c>
       <c r="F46" t="n">
-        <v>98.5</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.65 | kural_akts=2.37 (K_bilissel=1.20, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.97 | sapma=+98.5%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.50 | kural_akts=1.98 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.74 | sapma=+87.1%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9507107</t>
+          <t>735059</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Müzik-Mitoloji İlişkisi I</t>
+          <t>Yazma Eser Analizi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1868,138 +1868,138 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>3.9597</v>
+        <v>3.7402</v>
       </c>
       <c r="F47" t="n">
-        <v>97.98</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.78 | kural_akts=2.04 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.96 | sapma=+98.0%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.38 | kural_akts=2.25 (K_bilissel=1.14, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.74 | sapma=+87.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>725017</t>
+          <t>8201016</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Seminer 4</t>
+          <t>Sosyal Bilimlerde Yöntem II</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Siyasal Bilgiler</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.9264</v>
+        <v>3.7387</v>
       </c>
       <c r="F48" t="n">
-        <v>96.31999999999999</v>
+        <v>86.94</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.74 | kural_akts=2.04 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=1.02) | adaptif=3.93 | sapma=+96.3%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.29 | kural_akts=2.45 (K_bilissel=1.24, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.74 | sapma=+86.9%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>737013</t>
+          <t>103214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Görsel Algılama</t>
+          <t>Biyokimya Lab.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>3.9074</v>
+        <v>3.7359</v>
       </c>
       <c r="F49" t="n">
-        <v>95.37</v>
+        <v>86.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.63 | kural_akts=2.21 (K_bilissel=1.12, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.91 | sapma=+95.4%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.22 | kural_akts=2.60 (K_bilissel=1.16, K_profil=1.10, K_etkinlik=1.02) | adaptif=3.74 | sapma=+86.8%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>713176</t>
+          <t>205741</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sergi Hazırlama ve Küratoryel Çalışmalar II</t>
+          <t>İş Sağlığı ve Güvenliği</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Mühendislik</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>3.8971</v>
+        <v>3.7064</v>
       </c>
       <c r="F50" t="n">
-        <v>94.86</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.51 | kural_akts=2.47 (K_bilissel=1.25, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.90 | sapma=+94.9%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.18 | kural_akts=2.60 (K_bilissel=1.32, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.71 | sapma=+85.3%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>713173</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sergi Hazırlama ve Küratoryel Çalışmalar I</t>
+          <t>İş Sağlığı Ve Güvenliği II</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Güzel Sanatlar</t>
+          <t>Fen-Edebiyat</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.8971</v>
+        <v>3.7043</v>
       </c>
       <c r="F51" t="n">
-        <v>94.86</v>
+        <v>85.22</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AKTS_mevcut=2.0 | rf_tahmin=4.51 | kural_akts=2.47 (K_bilissel=1.25, K_profil=1.00, K_etkinlik=0.99) | adaptif=3.90 | sapma=+94.9%</t>
+          <t>AKTS_mevcut=2.0 | model_tahmin=4.55 | kural_akts=1.74 (K_bilissel=1.00, K_profil=1.00, K_etkinlik=0.87) | adaptif=3.70 | sapma=+85.2%</t>
         </is>
       </c>
     </row>
